--- a/fix/qa-validation-errors/ig/StructureDefinition-fr-cda-education-du-patient.xlsx
+++ b/fix/qa-validation-errors/ig/StructureDefinition-fr-cda-education-du-patient.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-01T12:39:31+00:00</t>
+    <t>2026-09-03T14:38:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fix/qa-validation-errors/ig/StructureDefinition-fr-cda-education-du-patient.xlsx
+++ b/fix/qa-validation-errors/ig/StructureDefinition-fr-cda-education-du-patient.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-03T14:38:58+00:00</t>
+    <t>2026-09-04T10:07:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fix/qa-validation-errors/ig/StructureDefinition-fr-cda-education-du-patient.xlsx
+++ b/fix/qa-validation-errors/ig/StructureDefinition-fr-cda-education-du-patient.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-04T10:07:56+00:00</t>
+    <t>2026-09-08T08:30:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fix/qa-validation-errors/ig/StructureDefinition-fr-cda-education-du-patient.xlsx
+++ b/fix/qa-validation-errors/ig/StructureDefinition-fr-cda-education-du-patient.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-08T08:30:09+00:00</t>
+    <t>2026-09-10T13:09:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
